--- a/branches/ci-version-start-page/ValueSet-mii-vs-labor-identifier-type-codes.xlsx
+++ b/branches/ci-version-start-page/ValueSet-mii-vs-labor-identifier-type-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T08:47:01+00:00</t>
+    <t>2026-10-09T09:03:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ci-version-start-page/ValueSet-mii-vs-labor-identifier-type-codes.xlsx
+++ b/branches/ci-version-start-page/ValueSet-mii-vs-labor-identifier-type-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T09:03:42+00:00</t>
+    <t>2026-10-09T10:05:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
